--- a/data/trans_orig/IP3110_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP3110_2023-Clase-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3096</t>
+          <t>3076</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11459</t>
+          <t>11610</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4952</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14634</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10285</t>
+          <t>9698</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22542</t>
+          <t>22852</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18032</t>
+          <t>18157</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32498</t>
+          <t>32976</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23270</t>
+          <t>23673</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43400</t>
+          <t>42695</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46348</t>
+          <t>46654</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>70171</t>
+          <t>71536</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>30,2%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39609</t>
+          <t>39641</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>57199</t>
+          <t>57602</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>50535</t>
+          <t>50165</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74832</t>
+          <t>75100</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>96618</t>
+          <t>95598</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>124296</t>
+          <t>125876</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>53,14%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8521</t>
+          <t>8682</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19915</t>
+          <t>20299</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14371</t>
+          <t>13493</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33904</t>
+          <t>33520</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26674</t>
+          <t>26059</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48653</t>
+          <t>48603</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,52%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8650</t>
+          <t>8873</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4948</t>
+          <t>4856</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15810</t>
+          <t>15931</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8190</t>
+          <t>8491</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21110</t>
+          <t>22428</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8070</t>
+          <t>8222</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>3474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8669</t>
+          <t>9237</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6684</t>
+          <t>6498</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15821</t>
+          <t>15291</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2213</t>
+          <t>2608</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12485</t>
+          <t>11529</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10610</t>
+          <t>10621</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23731</t>
+          <t>23735</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,69%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11505</t>
+          <t>12034</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24488</t>
+          <t>25094</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15535</t>
+          <t>15944</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30111</t>
+          <t>30162</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>31229</t>
+          <t>30705</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>50033</t>
+          <t>50913</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>27,21%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35489</t>
+          <t>35265</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51139</t>
+          <t>51486</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26574</t>
+          <t>27323</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43547</t>
+          <t>43736</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>66472</t>
+          <t>66596</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88600</t>
+          <t>90710</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>48,48%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>6164</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17333</t>
+          <t>16095</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13116</t>
+          <t>13144</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27066</t>
+          <t>27056</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>22309</t>
+          <t>21754</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>40109</t>
+          <t>38851</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>20,76%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5372</t>
+          <t>5022</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15617</t>
+          <t>15830</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5369</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15725</t>
+          <t>15191</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>13151</t>
+          <t>12776</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>27809</t>
+          <t>27118</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,49%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>391</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5874</t>
+          <t>6006</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>366</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6123</t>
+          <t>5529</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1524</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8960</t>
+          <t>8126</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>984</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7583</t>
+          <t>8322</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>577</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5012</t>
+          <t>4800</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2109</t>
+          <t>2424</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10147</t>
+          <t>10589</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9389</t>
+          <t>9351</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21449</t>
+          <t>20866</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17536</t>
+          <t>17902</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16828</t>
+          <t>16532</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33592</t>
+          <t>34279</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>30,49%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8754</t>
+          <t>7965</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18692</t>
+          <t>18375</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21497</t>
+          <t>21598</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>36114</t>
+          <t>35975</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>32553</t>
+          <t>32013</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>51399</t>
+          <t>50628</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,03%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7060</t>
+          <t>6401</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18186</t>
+          <t>17403</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6358</t>
+          <t>6659</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16878</t>
+          <t>17633</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14607</t>
+          <t>14807</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>30668</t>
+          <t>30206</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>26,87%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3571</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11742</t>
+          <t>12232</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5069</t>
+          <t>4721</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16488</t>
+          <t>16681</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10021</t>
+          <t>10456</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23836</t>
+          <t>24064</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,41%</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>4921</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6165</t>
+          <t>6047</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>924</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>8044</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8794</t>
+          <t>8460</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22955</t>
+          <t>22333</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6588</t>
+          <t>6705</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19812</t>
+          <t>19551</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18913</t>
+          <t>17780</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>38200</t>
+          <t>37281</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>24195</t>
+          <t>22458</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>51653</t>
+          <t>51940</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>16639</t>
+          <t>16348</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>32953</t>
+          <t>31937</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>46365</t>
+          <t>47426</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>76250</t>
+          <t>77955</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,24%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>45902</t>
+          <t>46897</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>91047</t>
+          <t>91037</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>85921</t>
+          <t>86185</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>116749</t>
+          <t>116714</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>142040</t>
+          <t>142142</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>197855</t>
+          <t>199106</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,59%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>43480</t>
+          <t>43317</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>124885</t>
+          <t>126118</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>32210</t>
+          <t>31921</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>54724</t>
+          <t>56208</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>83404</t>
+          <t>83483</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>175439</t>
+          <t>174799</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>40,9%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10987</t>
+          <t>11324</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26909</t>
+          <t>26656</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>20787</t>
+          <t>20613</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>47124</t>
+          <t>46256</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>36114</t>
+          <t>36018</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>68332</t>
+          <t>66740</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,62%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>882</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>6399</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>925</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7196</t>
+          <t>7166</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2392</t>
+          <t>2697</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9951</t>
+          <t>11332</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>2090</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>8896</t>
+          <t>9312</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>8874</t>
+          <t>8553</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>24425</t>
+          <t>24412</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>12494</t>
+          <t>12727</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>28554</t>
+          <t>28115</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>8505</t>
+          <t>8303</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>19585</t>
+          <t>20130</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>14910</t>
+          <t>14515</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>32839</t>
+          <t>31586</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>26358</t>
+          <t>25875</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>47343</t>
+          <t>46500</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,09%</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>46371</t>
+          <t>45611</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>64865</t>
+          <t>64709</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>41235</t>
+          <t>41023</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>67797</t>
+          <t>66001</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>91330</t>
+          <t>93361</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>125017</t>
+          <t>126012</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>46,3%</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>19015</t>
+          <t>18780</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>34330</t>
+          <t>33544</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>35075</t>
+          <t>34341</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>71754</t>
+          <t>70088</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>59262</t>
+          <t>58392</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>102620</t>
+          <t>98074</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>36,04%</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>9214</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>20944</t>
+          <t>20982</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>7166</t>
+          <t>7067</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>19233</t>
+          <t>20015</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>18643</t>
+          <t>18878</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>36146</t>
+          <t>36916</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>371</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>3980</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>2786</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>12098</t>
+          <t>12124</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3918</t>
+          <t>3902</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>13984</t>
+          <t>13918</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>4504</t>
+          <t>4629</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>390</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>6538</t>
+          <t>7296</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>798</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>7641</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -4818,12 +4818,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>6600</t>
+          <t>6997</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>17101</t>
+          <t>17244</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4833,12 +4833,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>6316</t>
+          <t>6048</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>17428</t>
+          <t>17068</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>15431</t>
+          <t>15313</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>30382</t>
+          <t>30246</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,24%</t>
         </is>
       </c>
     </row>
@@ -4931,12 +4931,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>23439</t>
+          <t>24114</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>37455</t>
+          <t>38218</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4966,12 +4966,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>16941</t>
+          <t>17169</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>31723</t>
+          <t>31549</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>45496</t>
+          <t>43921</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>66529</t>
+          <t>64741</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>47,6%</t>
         </is>
       </c>
     </row>
@@ -5044,12 +5044,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>6542</t>
+          <t>6518</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>16212</t>
+          <t>16276</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5059,12 +5059,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5079,12 +5079,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>20824</t>
+          <t>21779</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>17796</t>
+          <t>17495</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>33939</t>
+          <t>33662</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -5157,12 +5157,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>4875</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>14846</t>
+          <t>15234</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5172,12 +5172,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5192,12 +5192,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>7563</t>
+          <t>7254</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>19617</t>
+          <t>19728</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5227,12 +5227,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>14748</t>
+          <t>14875</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>29868</t>
+          <t>30589</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -5270,12 +5270,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1873</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>8594</t>
+          <t>8682</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5285,12 +5285,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5305,12 +5305,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1689</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>10290</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>4790</t>
+          <t>4618</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>15130</t>
+          <t>15144</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -5500,12 +5500,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>30405</t>
+          <t>30900</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>52829</t>
+          <t>51414</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5515,49 +5515,49 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
+          <t>4,82%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>8,02%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>45033</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>34669</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>60181</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>6,16%</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
           <t>4,74%</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="P46" s="2" t="inlineStr">
         <is>
           <t>8,24%</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>45033</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>34125</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>58241</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>6,16%</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>7,97%</t>
-        </is>
-      </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
           <t>127</t>
@@ -5570,12 +5570,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>69949</t>
+          <t>71882</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>103700</t>
+          <t>103598</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -5613,12 +5613,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>101058</t>
+          <t>100996</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>139638</t>
+          <t>138557</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5628,12 +5628,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>102246</t>
+          <t>103538</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>141144</t>
+          <t>141484</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>214656</t>
+          <t>214673</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>269693</t>
+          <t>268166</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,55%</t>
         </is>
       </c>
     </row>
@@ -5726,12 +5726,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>225096</t>
+          <t>228556</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>287624</t>
+          <t>289323</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>277032</t>
+          <t>276664</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>331028</t>
+          <t>332511</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>521365</t>
+          <t>525014</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>603732</t>
+          <t>609990</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>44,46%</t>
         </is>
       </c>
     </row>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>111505</t>
+          <t>110781</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>215088</t>
+          <t>209070</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>135186</t>
+          <t>136233</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>196332</t>
+          <t>191110</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5889,12 +5889,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>259130</t>
+          <t>258157</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>376917</t>
+          <t>370986</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,04%</t>
         </is>
       </c>
     </row>
@@ -5952,12 +5952,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>49297</t>
+          <t>49272</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>77417</t>
+          <t>76854</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>68613</t>
+          <t>67368</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>102705</t>
+          <t>103418</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6002,12 +6002,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>126020</t>
+          <t>125579</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>170160</t>
+          <t>172053</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>9126</t>
+          <t>9213</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>22508</t>
+          <t>22269</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6080,12 +6080,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>11631</t>
+          <t>12033</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>26711</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>24154</t>
+          <t>25078</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>44868</t>
+          <t>44531</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP3110_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP3110_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8126</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4400</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>13870</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,63%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>11,44%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6497</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3076</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11610</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,39%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,41%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8749</t>
+          <t>6089</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4615</t>
+          <t>2996</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14121</t>
+          <t>10896</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>15247</t>
+          <t>14215</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9698</t>
+          <t>8984</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22852</t>
+          <t>21487</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>30964</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>22789</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>40748</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>25,55%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>18,8%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>33,62%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>24890</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>18157</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>32976</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>24,47%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>17,85%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>32,42%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>32648</t>
+          <t>24659</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23673</t>
+          <t>18009</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42695</t>
+          <t>32242</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>57538</t>
+          <t>55623</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46654</t>
+          <t>45756</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>71536</t>
+          <t>67591</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,51%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>53761</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>43859</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>63344</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>44,35%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>36,18%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>52,26%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>48728</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>39641</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57602</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>47,91%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>38,97%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>56,63%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61714</t>
+          <t>46902</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>50165</t>
+          <t>38280</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>75100</t>
+          <t>55138</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>110443</t>
+          <t>100663</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>95598</t>
+          <t>87160</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>125876</t>
+          <t>112894</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>50,95%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>17596</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11476</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>24433</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>14,52%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>9,47%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>20,16%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>14039</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8682</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>20299</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>13,8%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8,54%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>19,96%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21853</t>
+          <t>14716</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13493</t>
+          <t>9529</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33520</t>
+          <t>21740</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>35892</t>
+          <t>32312</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26059</t>
+          <t>23415</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48603</t>
+          <t>41960</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>18,94%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10118</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5627</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>17329</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>8,35%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4,64%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4256</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1824</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8873</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,18%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8,72%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9488</t>
+          <t>4465</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4856</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15931</t>
+          <t>9697</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>13744</t>
+          <t>14583</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8491</t>
+          <t>8903</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22428</t>
+          <t>22613</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -1285,72 +1285,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>3658</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>3,02%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>3299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1070</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>8222</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>8,08%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>3518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>995</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3474</t>
+          <t>8421</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9237</t>
+          <t>9700</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -1398,74 +1398,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>100349</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>100349</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>100349</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>135176</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>135176</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>135176</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>319</t>
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1515,107 +1515,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5503</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2082</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>11582</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>6,12%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>12,89%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>10390</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>6498</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>15291</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>11,13%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>16,37%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5698</t>
+          <t>10163</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>5817</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11529</t>
+          <t>15016</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>15,74%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>15666</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>10074</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>22795</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>8,45%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>5,44%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>12,3%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>16088</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>10621</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>23735</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>8,6%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>5,68%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>12,69%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>20870</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>15255</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>27817</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>23,22%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>16,97%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>30,95%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>17744</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>12034</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>25094</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>19,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>12,89%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>26,87%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>22253</t>
+          <t>18253</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15944</t>
+          <t>12304</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30162</t>
+          <t>25237</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>39997</t>
+          <t>39123</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>30705</t>
+          <t>29987</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>50913</t>
+          <t>48716</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,29%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>32730</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>25137</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>41015</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>36,41%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>27,97%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>45,63%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>43074</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>35265</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>51486</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>46,12%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>37,76%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>55,13%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34701</t>
+          <t>43333</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27323</t>
+          <t>34530</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43736</t>
+          <t>51882</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>77776</t>
+          <t>76063</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>66596</t>
+          <t>65394</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90710</t>
+          <t>87347</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>47,14%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>18734</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>12768</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>27121</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>20,84%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>14,21%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>30,17%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>10462</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>6164</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>16095</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>11,2%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>6,6%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>17,23%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>19527</t>
+          <t>11242</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13144</t>
+          <t>6608</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27056</t>
+          <t>17301</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>29989</t>
+          <t>29976</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>21754</t>
+          <t>21636</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>38851</t>
+          <t>39274</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,2%</t>
         </is>
       </c>
     </row>
@@ -1967,72 +1967,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>10039</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>5617</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>16711</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>11,17%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>6,25%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>18,59%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>9577</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>5022</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>15830</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>10,25%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>5,38%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>16,95%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9673</t>
+          <t>10203</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5081</t>
+          <t>5388</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15191</t>
+          <t>16587</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>19249</t>
+          <t>20242</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>12776</t>
+          <t>13484</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>27118</t>
+          <t>29448</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2146</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>307</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6006</t>
+          <t>5877</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>674</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>6815</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>4220</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1524</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8126</t>
+          <t>8947</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -2193,74 +2193,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>95410</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>95410</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>95410</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>93708</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>93708</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>93708</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>265</t>
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3210</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>477</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8322</t>
+          <t>4292</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>818</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>4441</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2424</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10589</t>
+          <t>8888</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>7528</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3786</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>13140</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>13,48%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>6,78%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>23,53%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>14666</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>9351</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>20866</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>29,28%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>18,67%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>41,66%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9806</t>
+          <t>15208</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>9542</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17902</t>
+          <t>22526</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,22 +2498,22 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>24471</t>
+          <t>22735</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16532</t>
+          <t>15866</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34279</t>
+          <t>32083</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>29,75%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>25788</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>19236</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>32786</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>46,18%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>34,45%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>58,71%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>12979</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>7965</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>18375</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>25,91%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>15,9%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>36,69%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>28478</t>
+          <t>12942</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21598</t>
+          <t>8397</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35975</t>
+          <t>18637</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>41456</t>
+          <t>38729</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>32013</t>
+          <t>30194</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>50628</t>
+          <t>47268</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>43,83%</t>
         </is>
       </c>
     </row>
@@ -2649,72 +2649,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>6280</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>16981</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>18,27%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>11,25%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>30,41%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>11228</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>6401</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>17403</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>22,42%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>12,78%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>34,74%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10905</t>
+          <t>12544</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6659</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17633</t>
+          <t>20571</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>22133</t>
+          <t>22747</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14807</t>
+          <t>16154</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>30206</t>
+          <t>32204</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>29,86%</t>
         </is>
       </c>
     </row>
@@ -2762,72 +2762,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>9173</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>4946</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>15666</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>16,43%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>8,86%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>28,05%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>6744</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>3571</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>12232</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>13,46%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>7,13%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>24,42%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>9441</t>
+          <t>7228</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4721</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16681</t>
+          <t>12541</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>16184</t>
+          <t>16401</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10456</t>
+          <t>10626</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24064</t>
+          <t>24941</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>23,12%</t>
         </is>
       </c>
     </row>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2890,12 +2890,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4921</t>
+          <t>5740</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1732</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6047</t>
+          <t>4443</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2994</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>871</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>7441</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -2988,74 +2988,74 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>52010</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>52010</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>52010</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>62334</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>62334</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>62334</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>151</t>
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>8967</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>5042</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>14866</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>4,54%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>7,53%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>14820</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>8460</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>22333</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>6,9%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>3,94%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>10,4%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>11624</t>
+          <t>13813</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6705</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19551</t>
+          <t>20673</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>26444</t>
+          <t>22780</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17780</t>
+          <t>16617</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>37281</t>
+          <t>30973</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>22343</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>15864</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>31815</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>11,32%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>8,04%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>16,12%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>38103</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>22458</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>51940</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>17,75%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>10,46%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>24,19%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>23195</t>
+          <t>32941</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>16348</t>
+          <t>25564</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>31937</t>
+          <t>41487</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>61299</t>
+          <t>55284</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>47426</t>
+          <t>45143</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>77955</t>
+          <t>67180</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -3331,72 +3331,72 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>94430</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>81365</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>109081</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>47,86%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>41,24%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>55,28%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>73012</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>46897</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>91037</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>34,0%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>21,84%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>42,4%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>101580</t>
+          <t>67807</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>86185</t>
+          <t>57992</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>116714</t>
+          <t>78880</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>174592</t>
+          <t>162236</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>142142</t>
+          <t>145825</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>199106</t>
+          <t>180345</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>48,34%</t>
         </is>
       </c>
     </row>
@@ -3444,72 +3444,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>40246</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>29656</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>50544</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>20,4%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>15,03%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>25,62%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>67871</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>43317</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>126118</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>31,61%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>20,17%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>58,74%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>42983</t>
+          <t>40149</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>31921</t>
+          <t>31854</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>56208</t>
+          <t>50538</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>110854</t>
+          <t>80396</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>83483</t>
+          <t>67954</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>174799</t>
+          <t>96695</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -3557,72 +3557,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>28247</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>20183</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>44849</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>14,32%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>10,23%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>22,73%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>18470</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>11324</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>26656</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>8,6%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>12,41%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>30036</t>
+          <t>18654</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>20613</t>
+          <t>12528</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>46256</t>
+          <t>25954</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>48506</t>
+          <t>46900</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>36018</t>
+          <t>35385</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>66740</t>
+          <t>63204</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>16,94%</t>
         </is>
       </c>
     </row>
@@ -3670,72 +3670,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>3079</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>1242</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>7015</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>2436</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>882</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>6399</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3239</t>
+          <t>2403</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>605</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7166</t>
+          <t>6892</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>5676</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2697</t>
+          <t>2746</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>11332</t>
+          <t>10904</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -3783,74 +3783,74 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>214713</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>214713</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>214713</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>175767</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>175767</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>175767</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="P31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>212658</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>212658</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>212658</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>543</t>
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>427371</t>
+          <t>373079</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>427371</t>
+          <t>373079</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>427371</t>
+          <t>373079</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3900,72 +3900,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>12214</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>7099</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>19099</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>8,42%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>13,17%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>4640</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>2090</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>9312</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>8,14%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>14768</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>8553</t>
+          <t>1661</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>24412</t>
+          <t>7986</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>19408</t>
+          <t>16396</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>12727</t>
+          <t>10778</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>28115</t>
+          <t>23627</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -4013,72 +4013,72 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>20068</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>13693</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>28544</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>13,84%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>9,44%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>19,68%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>13405</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>8303</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>20130</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>11,72%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>7,26%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>17,6%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>22387</t>
+          <t>14017</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>14515</t>
+          <t>8851</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>31586</t>
+          <t>20603</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>35792</t>
+          <t>34085</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>25875</t>
+          <t>24000</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>46500</t>
+          <t>44337</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,08%</t>
         </is>
       </c>
     </row>
@@ -4126,72 +4126,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>51402</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>39456</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>64307</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>35,44%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>27,21%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>44,34%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>54816</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>45611</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>64709</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>47,92%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>39,87%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>56,57%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>54603</t>
+          <t>53532</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>41023</t>
+          <t>43940</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>66001</t>
+          <t>62155</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>109419</t>
+          <t>104934</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>93361</t>
+          <t>89423</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>126012</t>
+          <t>119662</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,11%</t>
         </is>
       </c>
     </row>
@@ -4239,72 +4239,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>42192</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>30372</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>63082</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>29,09%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>20,94%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>43,5%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>25873</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>18780</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>33544</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>22,62%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>16,42%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>29,33%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>47297</t>
+          <t>26804</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>34341</t>
+          <t>19816</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>70088</t>
+          <t>35029</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>73170</t>
+          <t>68996</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>58392</t>
+          <t>56136</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>98074</t>
+          <t>91958</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>35,43%</t>
         </is>
       </c>
     </row>
@@ -4352,72 +4352,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>12607</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>6970</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>20104</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>8,69%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>13,86%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>14246</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>9501</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>20982</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>12,45%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>8,31%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>18,34%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>12316</t>
+          <t>14800</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>7067</t>
+          <t>9278</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>20015</t>
+          <t>21707</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>26562</t>
+          <t>27407</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>18878</t>
+          <t>18506</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>36916</t>
+          <t>36360</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -4465,72 +4465,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>6541</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>2781</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>11746</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>4,51%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>8,1%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>1408</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>3980</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>6378</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2786</t>
+          <t>342</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>12124</t>
+          <t>3072</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>7786</t>
+          <t>7706</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3902</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>13918</t>
+          <t>14038</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -4578,74 +4578,74 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>145024</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>145024</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>145024</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>114387</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>114387</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>114387</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>114501</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>114501</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>114501</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="P38" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>157749</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>157749</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>157749</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
           <t>361</t>
@@ -4653,17 +4653,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>272136</t>
+          <t>259525</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>272136</t>
+          <t>259525</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>272136</t>
+          <t>259525</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4695,72 +4695,72 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>1519</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>4586</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>6,96%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>815</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>4629</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>4063</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>6,91%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>2222</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>7296</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>3,22%</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4770,32 +4770,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2209</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>619</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>7641</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -4808,72 +4808,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>9219</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>5189</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>15049</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>14,0%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>7,88%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>22,85%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>11192</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>6997</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>17244</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>16,71%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>10,45%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>25,75%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>10930</t>
+          <t>11777</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>6048</t>
+          <t>7324</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>17068</t>
+          <t>18074</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>22122</t>
+          <t>20996</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>15313</t>
+          <t>14832</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>30246</t>
+          <t>29433</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,94%</t>
         </is>
       </c>
     </row>
@@ -4921,72 +4921,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>15938</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>29883</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>34,1%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>24,2%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>45,37%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>30616</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>24114</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>38218</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>45,72%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>36,01%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>57,07%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>23860</t>
+          <t>30604</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>17169</t>
+          <t>23455</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>31549</t>
+          <t>38310</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4996,32 +4996,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>54476</t>
+          <t>53065</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>43921</t>
+          <t>42923</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>64741</t>
+          <t>63625</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,42%</t>
         </is>
       </c>
     </row>
@@ -5034,72 +5034,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>14962</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>9252</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>21430</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>22,72%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>14,05%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>32,54%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>10644</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>6518</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>16276</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>15,89%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>9,73%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>24,3%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>14731</t>
+          <t>10651</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>21779</t>
+          <t>16309</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5109,32 +5109,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>25375</t>
+          <t>25613</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>17495</t>
+          <t>17963</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>33662</t>
+          <t>34759</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>25,91%</t>
         </is>
       </c>
     </row>
@@ -5152,32 +5152,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>13120</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>7843</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>15234</t>
+          <t>20537</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5187,32 +5187,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>12565</t>
+          <t>10330</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>7254</t>
+          <t>6137</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>19728</t>
+          <t>16854</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5222,32 +5222,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>22000</t>
+          <t>23449</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>14875</t>
+          <t>16528</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>30589</t>
+          <t>34008</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>25,35%</t>
         </is>
       </c>
     </row>
@@ -5260,72 +5260,72 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>4582</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>1748</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>9643</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>6,96%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>14,64%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>4267</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>1909</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>8682</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>6,37%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>12,96%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>4724</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1656</t>
+          <t>1705</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>10290</t>
+          <t>9339</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5335,32 +5335,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>8990</t>
+          <t>8838</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>15144</t>
+          <t>15256</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -5373,74 +5373,74 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>66968</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>66968</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>66968</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>68306</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>68306</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>68306</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="O45" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="P45" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>69031</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>69031</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>69031</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
           <t>181</t>
@@ -5448,17 +5448,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>135999</t>
+          <t>134169</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>135999</t>
+          <t>134169</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>135999</t>
+          <t>134169</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5490,72 +5490,72 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>37951</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>28508</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>49530</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>5,62%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>4,22%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>7,34%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>40373</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>30900</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>51414</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>6,3%</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>37756</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>29235</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>48813</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>6,23%</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
         <is>
           <t>4,82%</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>8,02%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>45033</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>34669</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>60181</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>6,16%</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5565,32 +5565,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>85406</t>
+          <t>75708</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>71882</t>
+          <t>63418</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>103598</t>
+          <t>93287</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -5603,72 +5603,72 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>110992</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>94608</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>128966</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>16,44%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>14,01%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>19,1%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>119999</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>100996</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>138557</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>18,71%</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>15,75%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>21,61%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>121220</t>
+          <t>116854</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>103538</t>
+          <t>101565</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>141484</t>
+          <t>132884</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5678,32 +5678,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>241219</t>
+          <t>227847</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>214673</t>
+          <t>206057</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>268166</t>
+          <t>254222</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,84%</t>
         </is>
       </c>
     </row>
@@ -5716,72 +5716,72 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>383</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>280571</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>255629</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>305932</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>41,56%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>37,86%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>45,31%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>377</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>263224</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>228556</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>289323</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>41,05%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>35,64%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>45,12%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>383</t>
-        </is>
-      </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>304937</t>
+          <t>255119</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>276664</t>
+          <t>234324</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>332511</t>
+          <t>275035</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5791,32 +5791,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>568161</t>
+          <t>535690</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>525014</t>
+          <t>505344</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>609990</t>
+          <t>568380</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,35%</t>
         </is>
       </c>
     </row>
@@ -5829,72 +5829,72 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>143934</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>124816</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>169265</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>21,32%</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>18,49%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>25,07%</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>140117</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>110781</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>209070</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>21,85%</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>17,28%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>32,6%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>157297</t>
+          <t>116106</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>136233</t>
+          <t>99040</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>191110</t>
+          <t>132982</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5904,32 +5904,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>297413</t>
+          <t>260040</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>258157</t>
+          <t>234276</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>370986</t>
+          <t>290797</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>22,69%</t>
         </is>
       </c>
     </row>
@@ -5942,72 +5942,72 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>83303</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>68599</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>100163</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>12,34%</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>10,16%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>14,84%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>62726</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>49272</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>76854</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>9,78%</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>7,68%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>11,98%</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>83519</t>
+          <t>65680</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>67368</t>
+          <t>53526</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>103418</t>
+          <t>78955</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6017,32 +6017,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>146245</t>
+          <t>148982</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>125579</t>
+          <t>128773</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>172053</t>
+          <t>169792</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -6055,72 +6055,72 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>18382</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>12249</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>27094</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>2,72%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>4,01%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>14818</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>9213</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>22269</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>18652</t>
+          <t>14827</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>12033</t>
+          <t>9695</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>27511</t>
+          <t>22903</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6130,32 +6130,32 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>33470</t>
+          <t>33209</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>25078</t>
+          <t>24679</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>44531</t>
+          <t>44256</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -6168,74 +6168,74 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
+          <t>922</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>675133</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>675133</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>675133</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
           <t>898</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>641258</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>641258</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>641258</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>606342</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>606342</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>606342</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="O52" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
+      <c r="P52" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>922</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>730657</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>730657</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>730657</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
           <t>1820</t>
@@ -6243,17 +6243,17 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>1371914</t>
+          <t>1281475</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>1371914</t>
+          <t>1281475</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>1371914</t>
+          <t>1281475</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
